--- a/example_files/test.xlsx
+++ b/example_files/test.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="152">
   <si>
     <t>BORING_XID</t>
   </si>
@@ -97,6 +97,24 @@
     <t>CRS_ISOTACHE_C_validate</t>
   </si>
   <si>
+    <t>3740.0_AW207.+162_B_BIK_mo-19</t>
+  </si>
+  <si>
+    <t>fouten gevonden</t>
+  </si>
+  <si>
+    <t>was not in the range [0, 1000)</t>
+  </si>
+  <si>
+    <t>[-]</t>
+  </si>
+  <si>
+    <t>was not in the range [0, 0.1)</t>
+  </si>
+  <si>
+    <t>was not in the range [0, 1)</t>
+  </si>
+  <si>
     <t>SD_TERREINSPANNING</t>
   </si>
   <si>
@@ -127,9 +145,6 @@
     <t>SD_ISOTACHE_GRENSSPANNING_A_validate</t>
   </si>
   <si>
-    <t>geen data</t>
-  </si>
-  <si>
     <t>MONSTER_ID</t>
   </si>
   <si>
@@ -256,6 +271,48 @@
     <t>TXT_SS_REK_BIJ_T_EIND_validate</t>
   </si>
   <si>
+    <t>18.0_B02_18</t>
+  </si>
+  <si>
+    <t>19.0_B02_19</t>
+  </si>
+  <si>
+    <t>20.0_B02_20</t>
+  </si>
+  <si>
+    <t>21.0_B02_21</t>
+  </si>
+  <si>
+    <t>23.0_B02_23</t>
+  </si>
+  <si>
+    <t>25.0_B02_25</t>
+  </si>
+  <si>
+    <t>27.0_B01_27</t>
+  </si>
+  <si>
+    <t>28.0_B02_28</t>
+  </si>
+  <si>
+    <t>29.0_B02_29</t>
+  </si>
+  <si>
+    <t>30.0_B01_30</t>
+  </si>
+  <si>
+    <t>33.0_B01_33</t>
+  </si>
+  <si>
+    <t>1387.0_AW299.+003_B_BIT_M003-a</t>
+  </si>
+  <si>
+    <t>3715.0_AW207.+158_B_AL_mo-21</t>
+  </si>
+  <si>
+    <t>was not in the range [0, 2000)</t>
+  </si>
+  <si>
     <t>DSS_TERREINSPANNING</t>
   </si>
   <si>
@@ -368,6 +425,57 @@
   </si>
   <si>
     <t>DSS_REK_BIJ_T_EIND_validate</t>
+  </si>
+  <si>
+    <t>1.0_B01_1</t>
+  </si>
+  <si>
+    <t>2.0_B01_2</t>
+  </si>
+  <si>
+    <t>3.0_B01_3</t>
+  </si>
+  <si>
+    <t>4.0_B01_4</t>
+  </si>
+  <si>
+    <t>5.0_B02_5</t>
+  </si>
+  <si>
+    <t>6.0_B02_6</t>
+  </si>
+  <si>
+    <t>7.0_B01_7</t>
+  </si>
+  <si>
+    <t>8.0_B01_8</t>
+  </si>
+  <si>
+    <t>9.0_B02_9</t>
+  </si>
+  <si>
+    <t>10.0_B01_10</t>
+  </si>
+  <si>
+    <t>11.0_B01_11</t>
+  </si>
+  <si>
+    <t>12.0_B01_12</t>
+  </si>
+  <si>
+    <t>13.0_B01_13</t>
+  </si>
+  <si>
+    <t>14.0_B01_14</t>
+  </si>
+  <si>
+    <t>15.0_B01_15</t>
+  </si>
+  <si>
+    <t>16.0_B02_16</t>
+  </si>
+  <si>
+    <t>was not in the range [0, 60)</t>
   </si>
 </sst>
 </file>
@@ -841,7 +949,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K3"/>
+  <dimension ref="A1:K4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -884,16 +992,16 @@
         <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="H2" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="J2" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -904,16 +1012,45 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B4">
+        <v>127.2</v>
+      </c>
+      <c r="E4" t="s">
+        <v>27</v>
+      </c>
+      <c r="F4" t="s">
+        <v>28</v>
+      </c>
+      <c r="G4" t="s">
+        <v>29</v>
+      </c>
+      <c r="H4" t="s">
+        <v>28</v>
+      </c>
+      <c r="I4" t="s">
+        <v>30</v>
+      </c>
+      <c r="J4" t="s">
+        <v>28</v>
+      </c>
+      <c r="K4" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -928,34 +1065,34 @@
   <sheetData>
     <row r="1" spans="1:11">
       <c r="B1" s="1" t="s">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>33</v>
+        <v>39</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>34</v>
+        <v>40</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -963,19 +1100,19 @@
         <v>10</v>
       </c>
       <c r="B2" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="H2" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
       <c r="J2" t="s">
-        <v>35</v>
+        <v>12</v>
       </c>
     </row>
     <row r="3" spans="1:11">
@@ -1010,22 +1147,22 @@
   <sheetData>
     <row r="1" spans="1:7">
       <c r="B1" s="1" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>40</v>
+        <v>45</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
     <row r="2" spans="1:7">
@@ -1063,117 +1200,117 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AK3"/>
+  <dimension ref="A1:AK16"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:37">
       <c r="B1" s="1" t="s">
-        <v>42</v>
+        <v>47</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>43</v>
+        <v>48</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>44</v>
+        <v>49</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>51</v>
+        <v>56</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>53</v>
+        <v>58</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>58</v>
+        <v>63</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>59</v>
+        <v>64</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>64</v>
+        <v>69</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>69</v>
+        <v>74</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>73</v>
+        <v>78</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>74</v>
+        <v>79</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>77</v>
+        <v>82</v>
       </c>
     </row>
     <row r="2" spans="1:37">
@@ -1187,16 +1324,16 @@
         <v>12</v>
       </c>
       <c r="F2" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="H2" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="J2" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="L2" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="N2" t="s">
         <v>12</v>
@@ -1226,10 +1363,10 @@
         <v>12</v>
       </c>
       <c r="AF2" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="AH2" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="AJ2" t="s">
         <v>12</v>
@@ -1246,16 +1383,16 @@
         <v>0</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3">
         <v>0</v>
@@ -1285,13 +1422,786 @@
         <v>0</v>
       </c>
       <c r="AG3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK3">
         <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:37">
+      <c r="A4" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="B4">
+        <v>76.2</v>
+      </c>
+      <c r="D4">
+        <v>18.78746641387959</v>
+      </c>
+      <c r="G4" t="s">
+        <v>96</v>
+      </c>
+      <c r="I4" t="s">
+        <v>27</v>
+      </c>
+      <c r="J4">
+        <v>55.75503688224126</v>
+      </c>
+      <c r="L4">
+        <v>21.03055744626909</v>
+      </c>
+      <c r="N4">
+        <v>61.02092361226209</v>
+      </c>
+      <c r="P4">
+        <v>37.15420472864091</v>
+      </c>
+      <c r="R4">
+        <v>70.0286904116021</v>
+      </c>
+      <c r="T4">
+        <v>44.69716981508299</v>
+      </c>
+      <c r="V4">
+        <v>80.01349972014134</v>
+      </c>
+      <c r="X4">
+        <v>48.98023147380285</v>
+      </c>
+      <c r="Z4">
+        <v>80.31010732846335</v>
+      </c>
+      <c r="AB4">
+        <v>49.08167215896538</v>
+      </c>
+      <c r="AD4">
+        <v>15.68362503634125</v>
+      </c>
+      <c r="AF4">
+        <v>78.25439192779595</v>
+      </c>
+      <c r="AH4">
+        <v>46.71312687784666</v>
+      </c>
+      <c r="AJ4">
+        <v>25.00100000001839</v>
+      </c>
+    </row>
+    <row r="5" spans="1:37">
+      <c r="A5" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="B5">
+        <v>80.2</v>
+      </c>
+      <c r="D5">
+        <v>18.72532001844854</v>
+      </c>
+      <c r="G5" t="s">
+        <v>96</v>
+      </c>
+      <c r="I5" t="s">
+        <v>27</v>
+      </c>
+      <c r="J5">
+        <v>146.339210931561</v>
+      </c>
+      <c r="L5">
+        <v>55.95303125854116</v>
+      </c>
+      <c r="N5">
+        <v>139.060540309317</v>
+      </c>
+      <c r="P5">
+        <v>77.71824606848097</v>
+      </c>
+      <c r="R5">
+        <v>137.6365070410102</v>
+      </c>
+      <c r="T5">
+        <v>82.02076970804779</v>
+      </c>
+      <c r="V5">
+        <v>133.2841545187606</v>
+      </c>
+      <c r="X5">
+        <v>78.07745696489874</v>
+      </c>
+      <c r="Z5">
+        <v>139.5831209683092</v>
+      </c>
+      <c r="AB5">
+        <v>83.76080262998585</v>
+      </c>
+      <c r="AD5">
+        <v>7.060785567497078</v>
+      </c>
+      <c r="AF5">
+        <v>121.814612286631</v>
+      </c>
+      <c r="AH5">
+        <v>69.47016262914985</v>
+      </c>
+      <c r="AJ5">
+        <v>25.00262242319877</v>
+      </c>
+    </row>
+    <row r="6" spans="1:37">
+      <c r="A6" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="B6">
+        <v>78</v>
+      </c>
+      <c r="D6">
+        <v>18.59642912469585</v>
+      </c>
+      <c r="G6" t="s">
+        <v>96</v>
+      </c>
+      <c r="I6" t="s">
+        <v>27</v>
+      </c>
+      <c r="J6">
+        <v>164.9450498895021</v>
+      </c>
+      <c r="L6">
+        <v>61.9604749038117</v>
+      </c>
+      <c r="N6">
+        <v>153.9686607677517</v>
+      </c>
+      <c r="P6">
+        <v>81.19433163028434</v>
+      </c>
+      <c r="R6">
+        <v>143.9140161890874</v>
+      </c>
+      <c r="T6">
+        <v>82.23834154823435</v>
+      </c>
+      <c r="V6">
+        <v>146.8599379459108</v>
+      </c>
+      <c r="X6">
+        <v>84.52820534085865</v>
+      </c>
+      <c r="Z6">
+        <v>146.5539192449069</v>
+      </c>
+      <c r="AB6">
+        <v>85.0258189215092</v>
+      </c>
+      <c r="AD6">
+        <v>10.9972188276879</v>
+      </c>
+      <c r="AF6">
+        <v>141.134890475776</v>
+      </c>
+      <c r="AH6">
+        <v>78.43083353061229</v>
+      </c>
+      <c r="AJ6">
+        <v>25.00105347434874</v>
+      </c>
+    </row>
+    <row r="7" spans="1:37">
+      <c r="A7" s="1" t="s">
+        <v>86</v>
+      </c>
+      <c r="B7">
+        <v>77.59999999999999</v>
+      </c>
+      <c r="D7">
+        <v>17.00868825112868</v>
+      </c>
+      <c r="G7" t="s">
+        <v>96</v>
+      </c>
+      <c r="I7" t="s">
+        <v>27</v>
+      </c>
+      <c r="J7">
+        <v>55.29745696281316</v>
+      </c>
+      <c r="L7">
+        <v>21.50392387786997</v>
+      </c>
+      <c r="N7">
+        <v>55.99756496449875</v>
+      </c>
+      <c r="P7">
+        <v>35.19120712503734</v>
+      </c>
+      <c r="R7">
+        <v>58.71523663573423</v>
+      </c>
+      <c r="T7">
+        <v>39.50935241862763</v>
+      </c>
+      <c r="V7">
+        <v>60.97427895326799</v>
+      </c>
+      <c r="X7">
+        <v>40.38055026508041</v>
+      </c>
+      <c r="Z7">
+        <v>61.62796203285689</v>
+      </c>
+      <c r="AB7">
+        <v>41.20533773495117</v>
+      </c>
+      <c r="AD7">
+        <v>10.2282577498263</v>
+      </c>
+      <c r="AF7">
+        <v>59.17500717227813</v>
+      </c>
+      <c r="AH7">
+        <v>38.65115289704408</v>
+      </c>
+      <c r="AJ7">
+        <v>25.00311174930539</v>
+      </c>
+    </row>
+    <row r="8" spans="1:37">
+      <c r="A8" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B8">
+        <v>91.8</v>
+      </c>
+      <c r="D8">
+        <v>17.59792852073157</v>
+      </c>
+      <c r="G8" t="s">
+        <v>96</v>
+      </c>
+      <c r="I8" t="s">
+        <v>27</v>
+      </c>
+      <c r="J8">
+        <v>65.84156299685128</v>
+      </c>
+      <c r="L8">
+        <v>24.82449906482361</v>
+      </c>
+      <c r="N8">
+        <v>69.62088740216736</v>
+      </c>
+      <c r="P8">
+        <v>42.10213618092407</v>
+      </c>
+      <c r="R8">
+        <v>72.14471057354716</v>
+      </c>
+      <c r="T8">
+        <v>46.2631490283577</v>
+      </c>
+      <c r="V8">
+        <v>65.17444450152459</v>
+      </c>
+      <c r="X8">
+        <v>41.49107478726513</v>
+      </c>
+      <c r="Z8">
+        <v>72.31398905464448</v>
+      </c>
+      <c r="AB8">
+        <v>46.43139694980346</v>
+      </c>
+      <c r="AD8">
+        <v>5.402753978698456</v>
+      </c>
+      <c r="AF8">
+        <v>56.28135079314234</v>
+      </c>
+      <c r="AH8">
+        <v>34.69367636862444</v>
+      </c>
+      <c r="AJ8">
+        <v>25.00206102794618</v>
+      </c>
+    </row>
+    <row r="9" spans="1:37">
+      <c r="A9" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="B9">
+        <v>87.7</v>
+      </c>
+      <c r="D9">
+        <v>16.49089870964914</v>
+      </c>
+      <c r="G9" t="s">
+        <v>96</v>
+      </c>
+      <c r="I9" t="s">
+        <v>27</v>
+      </c>
+      <c r="J9">
+        <v>62.8013518807129</v>
+      </c>
+      <c r="L9">
+        <v>24.02147057192633</v>
+      </c>
+      <c r="N9">
+        <v>58.0851197405771</v>
+      </c>
+      <c r="P9">
+        <v>34.04207485914758</v>
+      </c>
+      <c r="R9">
+        <v>54.03370312991901</v>
+      </c>
+      <c r="T9">
+        <v>33.67555834650411</v>
+      </c>
+      <c r="V9">
+        <v>49.03838654895541</v>
+      </c>
+      <c r="X9">
+        <v>29.1479072010702</v>
+      </c>
+      <c r="Z9">
+        <v>56.1552309061517</v>
+      </c>
+      <c r="AB9">
+        <v>34.36959735193523</v>
+      </c>
+      <c r="AD9">
+        <v>3.284466137331037</v>
+      </c>
+      <c r="AF9">
+        <v>46.09356563782785</v>
+      </c>
+      <c r="AH9">
+        <v>26.15038213238586</v>
+      </c>
+      <c r="AJ9">
+        <v>25.00100000001839</v>
+      </c>
+    </row>
+    <row r="10" spans="1:37">
+      <c r="A10" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B10">
+        <v>84.3</v>
+      </c>
+      <c r="D10">
+        <v>17.83159750719408</v>
+      </c>
+      <c r="G10" t="s">
+        <v>96</v>
+      </c>
+      <c r="I10" t="s">
+        <v>27</v>
+      </c>
+      <c r="J10">
+        <v>142.3725291709416</v>
+      </c>
+      <c r="L10">
+        <v>53.83961966028437</v>
+      </c>
+      <c r="N10">
+        <v>133.7441417711594</v>
+      </c>
+      <c r="P10">
+        <v>79.27133379958057</v>
+      </c>
+      <c r="R10">
+        <v>128.2229393184744</v>
+      </c>
+      <c r="T10">
+        <v>81.96534834200546</v>
+      </c>
+      <c r="V10">
+        <v>122.9078127377535</v>
+      </c>
+      <c r="X10">
+        <v>77.240461551697</v>
+      </c>
+      <c r="Z10">
+        <v>127.9440441098996</v>
+      </c>
+      <c r="AB10">
+        <v>82.06993337720633</v>
+      </c>
+      <c r="AD10">
+        <v>5.194793052716705</v>
+      </c>
+      <c r="AF10">
+        <v>113.8573254694929</v>
+      </c>
+      <c r="AH10">
+        <v>69.77863552735653</v>
+      </c>
+      <c r="AJ10">
+        <v>25.00020617467817</v>
+      </c>
+    </row>
+    <row r="11" spans="1:37">
+      <c r="A11" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="B11">
+        <v>80.59999999999999</v>
+      </c>
+      <c r="D11">
+        <v>17.07877415012888</v>
+      </c>
+      <c r="G11" t="s">
+        <v>96</v>
+      </c>
+      <c r="I11" t="s">
+        <v>27</v>
+      </c>
+      <c r="J11">
+        <v>57.8883000050555</v>
+      </c>
+      <c r="L11">
+        <v>21.98519218683941</v>
+      </c>
+      <c r="N11">
+        <v>61.38059411686188</v>
+      </c>
+      <c r="P11">
+        <v>37.55551659853482</v>
+      </c>
+      <c r="R11">
+        <v>65.46663318063663</v>
+      </c>
+      <c r="T11">
+        <v>43.03816064512746</v>
+      </c>
+      <c r="V11">
+        <v>67.23634814836336</v>
+      </c>
+      <c r="X11">
+        <v>42.25839408515221</v>
+      </c>
+      <c r="Z11">
+        <v>67.45423085946823</v>
+      </c>
+      <c r="AB11">
+        <v>44.41461279016221</v>
+      </c>
+      <c r="AD11">
+        <v>7.104126476908277</v>
+      </c>
+      <c r="AF11">
+        <v>61.22230099100852</v>
+      </c>
+      <c r="AH11">
+        <v>35.46248218003893</v>
+      </c>
+      <c r="AJ11">
+        <v>25.00388316824683</v>
+      </c>
+    </row>
+    <row r="12" spans="1:37">
+      <c r="A12" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="B12">
+        <v>86.40000000000001</v>
+      </c>
+      <c r="D12">
+        <v>17.87274625433142</v>
+      </c>
+      <c r="G12" t="s">
+        <v>96</v>
+      </c>
+      <c r="I12" t="s">
+        <v>27</v>
+      </c>
+      <c r="J12">
+        <v>62.52489032089943</v>
+      </c>
+      <c r="L12">
+        <v>24.43229574669385</v>
+      </c>
+      <c r="N12">
+        <v>67.06488493754838</v>
+      </c>
+      <c r="P12">
+        <v>40.04210889701034</v>
+      </c>
+      <c r="R12">
+        <v>71.33465135889666</v>
+      </c>
+      <c r="T12">
+        <v>44.4368676128417</v>
+      </c>
+      <c r="V12">
+        <v>76.76337955459154</v>
+      </c>
+      <c r="X12">
+        <v>46.11587718484507</v>
+      </c>
+      <c r="Z12">
+        <v>75.61123609775677</v>
+      </c>
+      <c r="AB12">
+        <v>46.4680221346207</v>
+      </c>
+      <c r="AD12">
+        <v>10.81531827020808</v>
+      </c>
+      <c r="AF12">
+        <v>72.65628615574678</v>
+      </c>
+      <c r="AH12">
+        <v>41.32140319788596</v>
+      </c>
+      <c r="AJ12">
+        <v>25.00074004137423</v>
+      </c>
+    </row>
+    <row r="13" spans="1:37">
+      <c r="A13" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="B13">
+        <v>46.3</v>
+      </c>
+      <c r="D13">
+        <v>17.23719672825149</v>
+      </c>
+      <c r="G13" t="s">
+        <v>96</v>
+      </c>
+      <c r="I13" t="s">
+        <v>27</v>
+      </c>
+      <c r="J13">
+        <v>32.69704254323733</v>
+      </c>
+      <c r="L13">
+        <v>12.9590844179329</v>
+      </c>
+      <c r="N13">
+        <v>36.03583836119099</v>
+      </c>
+      <c r="P13">
+        <v>22.22706468948108</v>
+      </c>
+      <c r="R13">
+        <v>38.27278820611745</v>
+      </c>
+      <c r="T13">
+        <v>24.3169968942955</v>
+      </c>
+      <c r="V13">
+        <v>39.37851524061526</v>
+      </c>
+      <c r="X13">
+        <v>24.34489608171399</v>
+      </c>
+      <c r="Z13">
+        <v>39.90149452409241</v>
+      </c>
+      <c r="AB13">
+        <v>25.11289301942452</v>
+      </c>
+      <c r="AD13">
+        <v>8.58208566455869</v>
+      </c>
+      <c r="AF13">
+        <v>40.46928459580522</v>
+      </c>
+      <c r="AH13">
+        <v>24.35784399637487</v>
+      </c>
+      <c r="AJ13">
+        <v>25.00026047363644</v>
+      </c>
+    </row>
+    <row r="14" spans="1:37">
+      <c r="A14" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="B14">
+        <v>53.9</v>
+      </c>
+      <c r="D14">
+        <v>16.11604166704381</v>
+      </c>
+      <c r="G14" t="s">
+        <v>96</v>
+      </c>
+      <c r="I14" t="s">
+        <v>27</v>
+      </c>
+      <c r="J14">
+        <v>38.9144290467375</v>
+      </c>
+      <c r="L14">
+        <v>15.05654096190119</v>
+      </c>
+      <c r="N14">
+        <v>38.92138632583958</v>
+      </c>
+      <c r="P14">
+        <v>25.48586333700726</v>
+      </c>
+      <c r="R14">
+        <v>39.14075923129701</v>
+      </c>
+      <c r="T14">
+        <v>27.75925210171387</v>
+      </c>
+      <c r="V14">
+        <v>35.18421798153067</v>
+      </c>
+      <c r="X14">
+        <v>24.08507928829483</v>
+      </c>
+      <c r="Z14">
+        <v>39.27623111603316</v>
+      </c>
+      <c r="AB14">
+        <v>27.85076217664755</v>
+      </c>
+      <c r="AD14">
+        <v>5.827373047141009</v>
+      </c>
+      <c r="AF14">
+        <v>32.86511386101483</v>
+      </c>
+      <c r="AH14">
+        <v>20.84790807319223</v>
+      </c>
+      <c r="AJ14">
+        <v>25.00385859361268</v>
+      </c>
+    </row>
+    <row r="15" spans="1:37">
+      <c r="A15" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="B15">
+        <v>20.3</v>
+      </c>
+      <c r="D15">
+        <v>18.83</v>
+      </c>
+      <c r="G15" t="s">
+        <v>96</v>
+      </c>
+      <c r="I15" t="s">
+        <v>27</v>
+      </c>
+      <c r="K15" t="s">
+        <v>96</v>
+      </c>
+      <c r="M15" t="s">
+        <v>27</v>
+      </c>
+      <c r="N15">
+        <v>40.66</v>
+      </c>
+      <c r="P15">
+        <v>28.27</v>
+      </c>
+      <c r="R15">
+        <v>51.81</v>
+      </c>
+      <c r="T15">
+        <v>33.26</v>
+      </c>
+      <c r="V15">
+        <v>62.25</v>
+      </c>
+      <c r="X15">
+        <v>36.78</v>
+      </c>
+      <c r="Z15">
+        <v>64.14</v>
+      </c>
+      <c r="AB15">
+        <v>36.93</v>
+      </c>
+      <c r="AD15">
+        <v>19.04</v>
+      </c>
+      <c r="AF15">
+        <v>65.08</v>
+      </c>
+      <c r="AH15">
+        <v>36.33</v>
+      </c>
+      <c r="AJ15">
+        <v>25.1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:37">
+      <c r="A16" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="B16">
+        <v>26.6</v>
+      </c>
+      <c r="D16">
+        <v>12.300000190735</v>
+      </c>
+      <c r="F16">
+        <v>56.099998474121</v>
+      </c>
+      <c r="H16">
+        <v>18.10000038147</v>
+      </c>
+      <c r="J16">
+        <v>56.099998474121</v>
+      </c>
+      <c r="L16">
+        <v>18.10000038147</v>
+      </c>
+      <c r="N16">
+        <v>50.060001373291</v>
+      </c>
+      <c r="P16">
+        <v>33.360000610352</v>
+      </c>
+      <c r="R16">
+        <v>44.560001373291</v>
+      </c>
+      <c r="T16">
+        <v>33.959999084473</v>
+      </c>
+      <c r="V16">
+        <v>37.849998474121</v>
+      </c>
+      <c r="X16">
+        <v>29.14999961853</v>
+      </c>
+      <c r="Z16">
+        <v>44.790000915527</v>
+      </c>
+      <c r="AB16">
+        <v>33.990001678467</v>
+      </c>
+      <c r="AD16">
+        <v>4.780000209808</v>
+      </c>
+      <c r="AF16" t="s">
+        <v>28</v>
+      </c>
+      <c r="AG16" t="s">
+        <v>96</v>
+      </c>
+      <c r="AH16" t="s">
+        <v>28</v>
+      </c>
+      <c r="AI16" t="s">
+        <v>27</v>
+      </c>
+      <c r="AJ16">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1301,123 +2211,123 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AM3"/>
+  <dimension ref="A1:AM19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:39">
       <c r="B1" s="1" t="s">
-        <v>78</v>
+        <v>97</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>79</v>
+        <v>98</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>82</v>
+        <v>101</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>83</v>
+        <v>102</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>85</v>
+        <v>104</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>87</v>
+        <v>106</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>90</v>
+        <v>109</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>91</v>
+        <v>110</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>94</v>
+        <v>113</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>95</v>
+        <v>114</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>96</v>
+        <v>115</v>
       </c>
       <c r="U1" s="1" t="s">
-        <v>97</v>
+        <v>116</v>
       </c>
       <c r="V1" s="1" t="s">
-        <v>98</v>
+        <v>117</v>
       </c>
       <c r="W1" s="1" t="s">
-        <v>99</v>
+        <v>118</v>
       </c>
       <c r="X1" s="1" t="s">
-        <v>100</v>
+        <v>119</v>
       </c>
       <c r="Y1" s="1" t="s">
-        <v>101</v>
+        <v>120</v>
       </c>
       <c r="Z1" s="1" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="AA1" s="1" t="s">
-        <v>103</v>
+        <v>122</v>
       </c>
       <c r="AB1" s="1" t="s">
-        <v>104</v>
+        <v>123</v>
       </c>
       <c r="AC1" s="1" t="s">
-        <v>105</v>
+        <v>124</v>
       </c>
       <c r="AD1" s="1" t="s">
-        <v>106</v>
+        <v>125</v>
       </c>
       <c r="AE1" s="1" t="s">
-        <v>107</v>
+        <v>126</v>
       </c>
       <c r="AF1" s="1" t="s">
-        <v>108</v>
+        <v>127</v>
       </c>
       <c r="AG1" s="1" t="s">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="AH1" s="1" t="s">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="AI1" s="1" t="s">
-        <v>111</v>
+        <v>130</v>
       </c>
       <c r="AJ1" s="1" t="s">
-        <v>112</v>
+        <v>131</v>
       </c>
       <c r="AK1" s="1" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="AL1" s="1" t="s">
-        <v>114</v>
+        <v>133</v>
       </c>
       <c r="AM1" s="1" t="s">
-        <v>115</v>
+        <v>134</v>
       </c>
     </row>
     <row r="2" spans="1:39">
@@ -1428,7 +2338,7 @@
         <v>12</v>
       </c>
       <c r="D2" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
       <c r="F2" t="s">
         <v>12</v>
@@ -1479,7 +2389,7 @@
         <v>12</v>
       </c>
       <c r="AL2" t="s">
-        <v>12</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:39">
@@ -1490,7 +2400,7 @@
         <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G3">
         <v>0</v>
@@ -1541,7 +2451,1002 @@
         <v>0</v>
       </c>
       <c r="AM3">
-        <v>0</v>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:39">
+      <c r="A4" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B4">
+        <v>35.6</v>
+      </c>
+      <c r="E4" t="s">
+        <v>96</v>
+      </c>
+      <c r="F4">
+        <v>35.54339833940708</v>
+      </c>
+      <c r="H4">
+        <v>32.20934422381781</v>
+      </c>
+      <c r="J4">
+        <v>8.231123689118652</v>
+      </c>
+      <c r="L4">
+        <v>29.35158355331271</v>
+      </c>
+      <c r="N4">
+        <v>12.07981301858549</v>
+      </c>
+      <c r="P4">
+        <v>26.67243292471419</v>
+      </c>
+      <c r="R4">
+        <v>14.84011728585562</v>
+      </c>
+      <c r="T4">
+        <v>25.5114676523215</v>
+      </c>
+      <c r="V4">
+        <v>15.45883096326641</v>
+      </c>
+      <c r="X4">
+        <v>24.5886491024709</v>
+      </c>
+      <c r="Z4">
+        <v>15.09345949717159</v>
+      </c>
+      <c r="AB4">
+        <v>23.07046374626506</v>
+      </c>
+      <c r="AD4">
+        <v>15.72132092249539</v>
+      </c>
+      <c r="AF4">
+        <v>29.74241902136458</v>
+      </c>
+      <c r="AH4">
+        <v>21.99880349482565</v>
+      </c>
+      <c r="AJ4">
+        <v>13.80394306851458</v>
+      </c>
+      <c r="AL4">
+        <v>47.26912474155755</v>
+      </c>
+    </row>
+    <row r="5" spans="1:39">
+      <c r="A5" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="B5">
+        <v>37.1</v>
+      </c>
+      <c r="E5" t="s">
+        <v>96</v>
+      </c>
+      <c r="F5">
+        <v>36.55552191021097</v>
+      </c>
+      <c r="H5">
+        <v>34.56104310892095</v>
+      </c>
+      <c r="J5">
+        <v>7.573001558782679</v>
+      </c>
+      <c r="L5">
+        <v>31.6735140980981</v>
+      </c>
+      <c r="N5">
+        <v>13.46767980544128</v>
+      </c>
+      <c r="P5">
+        <v>29.29204687267719</v>
+      </c>
+      <c r="R5">
+        <v>19.25595144767878</v>
+      </c>
+      <c r="T5">
+        <v>27.56548313424703</v>
+      </c>
+      <c r="V5">
+        <v>20.96541137386387</v>
+      </c>
+      <c r="X5">
+        <v>26.49382288280762</v>
+      </c>
+      <c r="Z5">
+        <v>22.16798587586835</v>
+      </c>
+      <c r="AB5">
+        <v>23.90397727516238</v>
+      </c>
+      <c r="AD5">
+        <v>23.22092820886131</v>
+      </c>
+      <c r="AF5">
+        <v>33.21257961783439</v>
+      </c>
+      <c r="AH5">
+        <v>22.80254868340521</v>
+      </c>
+      <c r="AJ5">
+        <v>20.70845364483629</v>
+      </c>
+      <c r="AL5">
+        <v>48.06130573248407</v>
+      </c>
+    </row>
+    <row r="6" spans="1:39">
+      <c r="A6" s="1" t="s">
+        <v>137</v>
+      </c>
+      <c r="B6">
+        <v>38</v>
+      </c>
+      <c r="E6" t="s">
+        <v>96</v>
+      </c>
+      <c r="F6">
+        <v>37.5378771406971</v>
+      </c>
+      <c r="H6">
+        <v>33.63822455907035</v>
+      </c>
+      <c r="J6">
+        <v>7.248880230208549</v>
+      </c>
+      <c r="L6">
+        <v>31.49490405619153</v>
+      </c>
+      <c r="N6">
+        <v>11.39416329139244</v>
+      </c>
+      <c r="P6">
+        <v>29.79810865807913</v>
+      </c>
+      <c r="R6">
+        <v>15.3760098436623</v>
+      </c>
+      <c r="T6">
+        <v>28.72644840663973</v>
+      </c>
+      <c r="V6">
+        <v>16.23191908102397</v>
+      </c>
+      <c r="X6">
+        <v>26.9701163278918</v>
+      </c>
+      <c r="Z6">
+        <v>16.34414297352809</v>
+      </c>
+      <c r="AB6">
+        <v>23.72536723325581</v>
+      </c>
+      <c r="AD6">
+        <v>17.26853822657631</v>
+      </c>
+      <c r="AF6">
+        <v>28.86396498495447</v>
+      </c>
+      <c r="AH6">
+        <v>20.33177643703102</v>
+      </c>
+      <c r="AJ6">
+        <v>15.70511008429701</v>
+      </c>
+      <c r="AL6">
+        <v>42.88170698346946</v>
+      </c>
+    </row>
+    <row r="7" spans="1:39">
+      <c r="A7" s="1" t="s">
+        <v>138</v>
+      </c>
+      <c r="B7">
+        <v>37.4</v>
+      </c>
+      <c r="E7" t="s">
+        <v>96</v>
+      </c>
+      <c r="F7">
+        <v>36.55552191021097</v>
+      </c>
+      <c r="H7">
+        <v>35.51362999908932</v>
+      </c>
+      <c r="J7">
+        <v>7.840015172104665</v>
+      </c>
+      <c r="L7">
+        <v>33.69776123970587</v>
+      </c>
+      <c r="N7">
+        <v>13.85541507694656</v>
+      </c>
+      <c r="P7">
+        <v>31.49490405619153</v>
+      </c>
+      <c r="R7">
+        <v>19.96972801524948</v>
+      </c>
+      <c r="T7">
+        <v>29.53019359521928</v>
+      </c>
+      <c r="V7">
+        <v>22.691250350943</v>
+      </c>
+      <c r="X7">
+        <v>26.61289624407867</v>
+      </c>
+      <c r="Z7">
+        <v>22.01944862161687</v>
+      </c>
+      <c r="AB7">
+        <v>23.63606221230253</v>
+      </c>
+      <c r="AD7">
+        <v>23.59172037079059</v>
+      </c>
+      <c r="AF7">
+        <v>36.90052599009901</v>
+      </c>
+      <c r="AH7">
+        <v>22.86208536404073</v>
+      </c>
+      <c r="AJ7">
+        <v>22.11687947008851</v>
+      </c>
+      <c r="AL7">
+        <v>46.63134282178218</v>
+      </c>
+    </row>
+    <row r="8" spans="1:39">
+      <c r="A8" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B8">
+        <v>94.34</v>
+      </c>
+      <c r="E8" t="s">
+        <v>96</v>
+      </c>
+      <c r="F8">
+        <v>93.93332832737153</v>
+      </c>
+      <c r="H8">
+        <v>84.98260873565393</v>
+      </c>
+      <c r="J8">
+        <v>22.47412710985237</v>
+      </c>
+      <c r="L8">
+        <v>88.30731765617938</v>
+      </c>
+      <c r="N8">
+        <v>36.38347241417794</v>
+      </c>
+      <c r="P8">
+        <v>87.4491560069268</v>
+      </c>
+      <c r="R8">
+        <v>45.59016352030992</v>
+      </c>
+      <c r="T8">
+        <v>82.45537792363051</v>
+      </c>
+      <c r="V8">
+        <v>49.53871440948296</v>
+      </c>
+      <c r="X8">
+        <v>86.59693612210721</v>
+      </c>
+      <c r="Z8">
+        <v>49.38938925424176</v>
+      </c>
+      <c r="AB8">
+        <v>83.45943516626659</v>
+      </c>
+      <c r="AD8">
+        <v>49.73840477130715</v>
+      </c>
+      <c r="AF8">
+        <v>17.40566543937173</v>
+      </c>
+      <c r="AH8">
+        <v>70.68993744437684</v>
+      </c>
+      <c r="AJ8">
+        <v>43.3815385065007</v>
+      </c>
+      <c r="AL8">
+        <v>42.9931055704939</v>
+      </c>
+    </row>
+    <row r="9" spans="1:39">
+      <c r="A9" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="B9">
+        <v>108.36</v>
+      </c>
+      <c r="E9" t="s">
+        <v>96</v>
+      </c>
+      <c r="F9">
+        <v>107.9058870364126</v>
+      </c>
+      <c r="H9">
+        <v>107.9181012752174</v>
+      </c>
+      <c r="J9">
+        <v>23.25359242257993</v>
+      </c>
+      <c r="L9">
+        <v>107.6795655007229</v>
+      </c>
+      <c r="N9">
+        <v>40.62032400514454</v>
+      </c>
+      <c r="P9">
+        <v>103.2639388440235</v>
+      </c>
+      <c r="R9">
+        <v>52.14654010343214</v>
+      </c>
+      <c r="T9">
+        <v>100.5706884192143</v>
+      </c>
+      <c r="V9">
+        <v>55.70192149022767</v>
+      </c>
+      <c r="X9">
+        <v>94.99745313752899</v>
+      </c>
+      <c r="Z9">
+        <v>55.83093124259294</v>
+      </c>
+      <c r="AB9">
+        <v>96.58574625179966</v>
+      </c>
+      <c r="AD9">
+        <v>56.17494285006018</v>
+      </c>
+      <c r="AF9">
+        <v>18.26218448295917</v>
+      </c>
+      <c r="AH9">
+        <v>80.77544083797622</v>
+      </c>
+      <c r="AJ9">
+        <v>43.77726359892907</v>
+      </c>
+      <c r="AL9">
+        <v>47.81599093568386</v>
+      </c>
+    </row>
+    <row r="10" spans="1:39">
+      <c r="A10" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="B10">
+        <v>51.9</v>
+      </c>
+      <c r="E10" t="s">
+        <v>96</v>
+      </c>
+      <c r="F10">
+        <v>51.38015538845613</v>
+      </c>
+      <c r="H10">
+        <v>47.48050280682939</v>
+      </c>
+      <c r="J10">
+        <v>10.70346677994699</v>
+      </c>
+      <c r="L10">
+        <v>44.11668035092235</v>
+      </c>
+      <c r="N10">
+        <v>17.91405972024565</v>
+      </c>
+      <c r="P10">
+        <v>40.60401619342651</v>
+      </c>
+      <c r="R10">
+        <v>22.75876876245662</v>
+      </c>
+      <c r="T10">
+        <v>38.78814743404307</v>
+      </c>
+      <c r="V10">
+        <v>23.6745815219918</v>
+      </c>
+      <c r="X10">
+        <v>35.6029350200426</v>
+      </c>
+      <c r="Z10">
+        <v>22.68495818155589</v>
+      </c>
+      <c r="AB10">
+        <v>39.35374590008054</v>
+      </c>
+      <c r="AD10">
+        <v>23.91432191506909</v>
+      </c>
+      <c r="AF10">
+        <v>13.18728690676804</v>
+      </c>
+      <c r="AH10">
+        <v>30.7506955482475</v>
+      </c>
+      <c r="AJ10">
+        <v>20.78687256550386</v>
+      </c>
+      <c r="AL10">
+        <v>43.01054199161344</v>
+      </c>
+    </row>
+    <row r="11" spans="1:39">
+      <c r="A11" s="1" t="s">
+        <v>142</v>
+      </c>
+      <c r="B11">
+        <v>40.1</v>
+      </c>
+      <c r="E11" t="s">
+        <v>96</v>
+      </c>
+      <c r="F11">
+        <v>153.0985742542467</v>
+      </c>
+      <c r="H11">
+        <v>147.5021262745076</v>
+      </c>
+      <c r="J11">
+        <v>21.17655747865349</v>
+      </c>
+      <c r="L11">
+        <v>135.6840951683563</v>
+      </c>
+      <c r="N11">
+        <v>41.86677587190128</v>
+      </c>
+      <c r="P11">
+        <v>123.5386123187097</v>
+      </c>
+      <c r="R11">
+        <v>54.67965159366746</v>
+      </c>
+      <c r="T11">
+        <v>116.6621257053068</v>
+      </c>
+      <c r="V11">
+        <v>60.49696734075972</v>
+      </c>
+      <c r="X11">
+        <v>112.4945580608202</v>
+      </c>
+      <c r="Z11">
+        <v>64.14159185791802</v>
+      </c>
+      <c r="AB11">
+        <v>107.8506969712494</v>
+      </c>
+      <c r="AD11">
+        <v>67.35782351725567</v>
+      </c>
+      <c r="AF11">
+        <v>26.01326030556356</v>
+      </c>
+      <c r="AH11">
+        <v>90.97204801107875</v>
+      </c>
+      <c r="AJ11">
+        <v>65.06353151590108</v>
+      </c>
+      <c r="AL11">
+        <v>46.76275583741712</v>
+      </c>
+    </row>
+    <row r="12" spans="1:39">
+      <c r="A12" s="1" t="s">
+        <v>143</v>
+      </c>
+      <c r="B12">
+        <v>94.09999999999999</v>
+      </c>
+      <c r="E12" t="s">
+        <v>96</v>
+      </c>
+      <c r="F12">
+        <v>250.9217354092689</v>
+      </c>
+      <c r="H12">
+        <v>239.3251184482556</v>
+      </c>
+      <c r="J12">
+        <v>33.55231157368264</v>
+      </c>
+      <c r="L12">
+        <v>223.800900135956</v>
+      </c>
+      <c r="N12">
+        <v>61.36712327367944</v>
+      </c>
+      <c r="P12">
+        <v>210.3184762692781</v>
+      </c>
+      <c r="R12">
+        <v>81.68427038625509</v>
+      </c>
+      <c r="T12">
+        <v>202.8864494603039</v>
+      </c>
+      <c r="V12">
+        <v>91.21705514825318</v>
+      </c>
+      <c r="X12">
+        <v>197.3023387077934</v>
+      </c>
+      <c r="Z12">
+        <v>97.4540644932901</v>
+      </c>
+      <c r="AB12">
+        <v>191.9433282753775</v>
+      </c>
+      <c r="AD12">
+        <v>101.3857616696341</v>
+      </c>
+      <c r="AF12">
+        <v>29.43731096905709</v>
+      </c>
+      <c r="AH12">
+        <v>163.9540038918882</v>
+      </c>
+      <c r="AJ12">
+        <v>89.68751050002889</v>
+      </c>
+      <c r="AL12">
+        <v>61.00617085627555</v>
+      </c>
+      <c r="AM12" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="13" spans="1:39">
+      <c r="A13" s="1" t="s">
+        <v>144</v>
+      </c>
+      <c r="B13">
+        <v>58</v>
+      </c>
+      <c r="E13" t="s">
+        <v>96</v>
+      </c>
+      <c r="F13">
+        <v>154.0809294847328</v>
+      </c>
+      <c r="H13">
+        <v>143.7513153944697</v>
+      </c>
+      <c r="J13">
+        <v>26.89607202553196</v>
+      </c>
+      <c r="L13">
+        <v>133.7193847073841</v>
+      </c>
+      <c r="N13">
+        <v>40.50757737325273</v>
+      </c>
+      <c r="P13">
+        <v>124.0744424444294</v>
+      </c>
+      <c r="R13">
+        <v>51.8722661180308</v>
+      </c>
+      <c r="T13">
+        <v>116.6918940456246</v>
+      </c>
+      <c r="V13">
+        <v>56.59829842933435</v>
+      </c>
+      <c r="X13">
+        <v>112.0480329560538</v>
+      </c>
+      <c r="Z13">
+        <v>59.00240019585252</v>
+      </c>
+      <c r="AB13">
+        <v>103.7128976670806</v>
+      </c>
+      <c r="AD13">
+        <v>59.47546503009579</v>
+      </c>
+      <c r="AF13">
+        <v>28.48765724013998</v>
+      </c>
+      <c r="AH13">
+        <v>92.10324494315368</v>
+      </c>
+      <c r="AJ13">
+        <v>56.51520137967926</v>
+      </c>
+      <c r="AL13">
+        <v>42.47138938806393</v>
+      </c>
+    </row>
+    <row r="14" spans="1:39">
+      <c r="A14" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="B14">
+        <v>54.4</v>
+      </c>
+      <c r="E14" t="s">
+        <v>96</v>
+      </c>
+      <c r="F14">
+        <v>53.34486584942838</v>
+      </c>
+      <c r="H14">
+        <v>52.0945955560824</v>
+      </c>
+      <c r="J14">
+        <v>14.21077411691303</v>
+      </c>
+      <c r="L14">
+        <v>46.31953753443669</v>
+      </c>
+      <c r="N14">
+        <v>27.96510382849757</v>
+      </c>
+      <c r="P14">
+        <v>40.21702776929561</v>
+      </c>
+      <c r="R14">
+        <v>32.83024477964177</v>
+      </c>
+      <c r="T14">
+        <v>35.18617825559394</v>
+      </c>
+      <c r="V14">
+        <v>32.15793601322344</v>
+      </c>
+      <c r="X14">
+        <v>34.5312747686032</v>
+      </c>
+      <c r="Z14">
+        <v>33.7775202420433</v>
+      </c>
+      <c r="AB14">
+        <v>35.03733655400514</v>
+      </c>
+      <c r="AD14">
+        <v>33.96477598158817</v>
+      </c>
+      <c r="AF14">
+        <v>17.71020376297915</v>
+      </c>
+      <c r="AH14">
+        <v>31.82235579968691</v>
+      </c>
+      <c r="AJ14">
+        <v>30.88523941277428</v>
+      </c>
+      <c r="AL14">
+        <v>47.25583574049496</v>
+      </c>
+    </row>
+    <row r="15" spans="1:39">
+      <c r="A15" s="1" t="s">
+        <v>146</v>
+      </c>
+      <c r="B15">
+        <v>58.6</v>
+      </c>
+      <c r="E15" t="s">
+        <v>96</v>
+      </c>
+      <c r="F15">
+        <v>58.28641034217677</v>
+      </c>
+      <c r="H15">
+        <v>54.98212456690526</v>
+      </c>
+      <c r="J15">
+        <v>14.63205577507889</v>
+      </c>
+      <c r="L15">
+        <v>48.76054144049313</v>
+      </c>
+      <c r="N15">
+        <v>28.06443377740887</v>
+      </c>
+      <c r="P15">
+        <v>42.83664171725862</v>
+      </c>
+      <c r="R15">
+        <v>33.98174511291224</v>
+      </c>
+      <c r="T15">
+        <v>37.65695050196813</v>
+      </c>
+      <c r="V15">
+        <v>33.34949882399913</v>
+      </c>
+      <c r="X15">
+        <v>32.77494268985527</v>
+      </c>
+      <c r="Z15">
+        <v>31.37689308902333</v>
+      </c>
+      <c r="AB15">
+        <v>40.4551744918377</v>
+      </c>
+      <c r="AD15">
+        <v>34.51844874749153</v>
+      </c>
+      <c r="AF15">
+        <v>12.6439923464407</v>
+      </c>
+      <c r="AH15">
+        <v>33.42984617684602</v>
+      </c>
+      <c r="AJ15">
+        <v>31.93159130586062</v>
+      </c>
+      <c r="AL15">
+        <v>43.28556366902261</v>
+      </c>
+    </row>
+    <row r="16" spans="1:39">
+      <c r="A16" s="1" t="s">
+        <v>147</v>
+      </c>
+      <c r="B16">
+        <v>65</v>
+      </c>
+      <c r="E16" t="s">
+        <v>96</v>
+      </c>
+      <c r="F16">
+        <v>64.21031006541128</v>
+      </c>
+      <c r="H16">
+        <v>62.06698956253246</v>
+      </c>
+      <c r="J16">
+        <v>12.30591619986504</v>
+      </c>
+      <c r="L16">
+        <v>57.09567672946631</v>
+      </c>
+      <c r="N16">
+        <v>25.01850625273351</v>
+      </c>
+      <c r="P16">
+        <v>52.68996236243763</v>
+      </c>
+      <c r="R16">
+        <v>34.94332731796069</v>
+      </c>
+      <c r="T16">
+        <v>50.27872679669895</v>
+      </c>
+      <c r="V16">
+        <v>39.09337452314249</v>
+      </c>
+      <c r="X16">
+        <v>48.28424799540895</v>
+      </c>
+      <c r="Z16">
+        <v>40.95125952385668</v>
+      </c>
+      <c r="AB16">
+        <v>48.87961480176418</v>
+      </c>
+      <c r="AD16">
+        <v>41.13860029692367</v>
+      </c>
+      <c r="AF16">
+        <v>18.57849196538937</v>
+      </c>
+      <c r="AH16">
+        <v>39.44305092103382</v>
+      </c>
+      <c r="AJ16">
+        <v>36.91797056645259</v>
+      </c>
+      <c r="AL16">
+        <v>45.67779151215493</v>
+      </c>
+    </row>
+    <row r="17" spans="1:38">
+      <c r="A17" s="1" t="s">
+        <v>148</v>
+      </c>
+      <c r="B17">
+        <v>65.5</v>
+      </c>
+      <c r="E17" t="s">
+        <v>96</v>
+      </c>
+      <c r="F17">
+        <v>65.1926652958974</v>
+      </c>
+      <c r="H17">
+        <v>60.78695092886872</v>
+      </c>
+      <c r="J17">
+        <v>14.06642561761414</v>
+      </c>
+      <c r="L17">
+        <v>54.83328286531645</v>
+      </c>
+      <c r="N17">
+        <v>23.65954855300746</v>
+      </c>
+      <c r="P17">
+        <v>49.6238233097082</v>
+      </c>
+      <c r="R17">
+        <v>29.36694696753188</v>
+      </c>
+      <c r="T17">
+        <v>44.02737532996907</v>
+      </c>
+      <c r="V17">
+        <v>28.82483484219935</v>
+      </c>
+      <c r="X17">
+        <v>36.40668020862216</v>
+      </c>
+      <c r="Z17">
+        <v>24.9175853131934</v>
+      </c>
+      <c r="AB17">
+        <v>47.21258774396954</v>
+      </c>
+      <c r="AD17">
+        <v>30.28244194512239</v>
+      </c>
+      <c r="AF17">
+        <v>12.77699198491278</v>
+      </c>
+      <c r="AH17">
+        <v>34.56104310892095</v>
+      </c>
+      <c r="AJ17">
+        <v>24.89063575196912</v>
+      </c>
+      <c r="AL17">
+        <v>47.07685054219706</v>
+      </c>
+    </row>
+    <row r="18" spans="1:38">
+      <c r="A18" s="1" t="s">
+        <v>149</v>
+      </c>
+      <c r="B18">
+        <v>72.2</v>
+      </c>
+      <c r="E18" t="s">
+        <v>96</v>
+      </c>
+      <c r="F18">
+        <v>71.11656501913191</v>
+      </c>
+      <c r="H18">
+        <v>70.01513642737474</v>
+      </c>
+      <c r="J18">
+        <v>16.94945889473087</v>
+      </c>
+      <c r="L18">
+        <v>63.61494325905606</v>
+      </c>
+      <c r="N18">
+        <v>36.71779824553304</v>
+      </c>
+      <c r="P18">
+        <v>56.44077324247556</v>
+      </c>
+      <c r="R18">
+        <v>46.19620840950906</v>
+      </c>
+      <c r="T18">
+        <v>41.31845636105279</v>
+      </c>
+      <c r="V18">
+        <v>37.63473300276061</v>
+      </c>
+      <c r="X18">
+        <v>42.538958314081</v>
+      </c>
+      <c r="Z18">
+        <v>43.36260362485978</v>
+      </c>
+      <c r="AB18">
+        <v>43.04502009948295</v>
+      </c>
+      <c r="AD18">
+        <v>46.87477598699388</v>
+      </c>
+      <c r="AF18">
+        <v>28.63831294015816</v>
+      </c>
+      <c r="AH18">
+        <v>37.95463390514575</v>
+      </c>
+      <c r="AJ18">
+        <v>36.64038972982777</v>
+      </c>
+      <c r="AL18">
+        <v>43.65975528189794</v>
+      </c>
+    </row>
+    <row r="19" spans="1:38">
+      <c r="A19" s="1" t="s">
+        <v>150</v>
+      </c>
+      <c r="B19">
+        <v>112.93</v>
+      </c>
+      <c r="E19" t="s">
+        <v>96</v>
+      </c>
+      <c r="F19">
+        <v>112.91706232935</v>
+      </c>
+      <c r="H19">
+        <v>108.9812783074681</v>
+      </c>
+      <c r="J19">
+        <v>27.46501106032071</v>
+      </c>
+      <c r="L19">
+        <v>106.0208322309806</v>
+      </c>
+      <c r="N19">
+        <v>43.77048602232016</v>
+      </c>
+      <c r="P19">
+        <v>102.3718153075362</v>
+      </c>
+      <c r="R19">
+        <v>54.96251875596452</v>
+      </c>
+      <c r="T19">
+        <v>97.61470216551834</v>
+      </c>
+      <c r="V19">
+        <v>58.68135430866637</v>
+      </c>
+      <c r="X19">
+        <v>94.13747706520333</v>
+      </c>
+      <c r="Z19">
+        <v>58.38923796881076</v>
+      </c>
+      <c r="AB19">
+        <v>96.04263210536912</v>
+      </c>
+      <c r="AD19">
+        <v>59.06666191963023</v>
+      </c>
+      <c r="AF19">
+        <v>16.76831822523081</v>
+      </c>
+      <c r="AH19">
+        <v>80.71544567063796</v>
+      </c>
+      <c r="AJ19">
+        <v>43.08288837354917</v>
+      </c>
+      <c r="AL19">
+        <v>46.17466195271527</v>
       </c>
     </row>
   </sheetData>
